--- a/Compo D1 .xlsx
+++ b/Compo D1 .xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="LAVAL" sheetId="1" state="visible" r:id="rId3"/>
@@ -14,6 +14,8 @@
     <sheet name="TOULON" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="MTP" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="NMF" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="UJS" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="SPORTING" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="104">
   <si>
     <t xml:space="preserve">Nom d’équipe </t>
   </si>
@@ -265,6 +267,78 @@
   </si>
   <si>
     <t xml:space="preserve">SACKO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UJS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOUIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZZAKHNINI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOUITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I.AHSSEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERRADDAF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOURI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y.AHSSEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOHAMED ADAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARRADY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIAOUNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPORTING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOKOKA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEHDAOUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AISSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARECO GALENO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARECO GALEANO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCHAPTCHET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BELHAJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAHANI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMARILLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUKUTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAIO</t>
   </si>
 </sst>
 </file>
@@ -340,7 +414,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -353,8 +427,24 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1384,7 +1474,7 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="18.87"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1411,7 +1501,7 @@
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="2" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1492,7 +1582,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>75</v>
       </c>
@@ -1538,6 +1628,359 @@
       <c r="C14" s="1" t="n">
         <v>23</v>
       </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="18.87"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" s="7" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="18.87"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1"/>

--- a/Compo D1 .xlsx
+++ b/Compo D1 .xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="LAVAL" sheetId="1" state="visible" r:id="rId3"/>
@@ -16,6 +16,7 @@
     <sheet name="NMF" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="UJS" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="SPORTING" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="ACASA" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="121">
   <si>
     <t xml:space="preserve">Nom d’équipe </t>
   </si>
@@ -239,6 +240,9 @@
     <t xml:space="preserve">BOTELLA</t>
   </si>
   <si>
+    <t xml:space="preserve">HULA</t>
+  </si>
+  <si>
     <t xml:space="preserve">EL HOKARI</t>
   </si>
   <si>
@@ -254,12 +258,12 @@
     <t xml:space="preserve">VALDELVIRA</t>
   </si>
   <si>
+    <t xml:space="preserve">LEONARDO ALMEIDA ROSA </t>
+  </si>
+  <si>
     <t xml:space="preserve">LEOZINHO</t>
   </si>
   <si>
-    <t xml:space="preserve">LEONARDO ALMEIDA ROSA </t>
-  </si>
-  <si>
     <t xml:space="preserve">BENDALI</t>
   </si>
   <si>
@@ -269,6 +273,12 @@
     <t xml:space="preserve">SACKO</t>
   </si>
   <si>
+    <t xml:space="preserve">SANTAGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RABOU</t>
+  </si>
+  <si>
     <t xml:space="preserve">UJS</t>
   </si>
   <si>
@@ -339,6 +349,48 @@
   </si>
   <si>
     <t xml:space="preserve">CAIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACASA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABOUDOU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI CHAIB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALAOUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO. SOUMARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIARRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAHMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI. SOUMARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOURE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIAUD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIRTYS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. SI CHAIB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIANKA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLIMSI</t>
   </si>
 </sst>
 </file>
@@ -414,7 +466,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -427,12 +479,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -447,7 +503,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1471,10 +1527,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="18.87"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="1" style="3" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.87"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="3" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1501,7 +1559,7 @@
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1528,36 +1586,36 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="n">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1" t="n">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>7</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1568,7 +1626,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1579,10 +1637,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>75</v>
       </c>
@@ -1590,9 +1648,9 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="D11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1604,7 +1662,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1615,7 +1673,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1626,13 +1684,41 @@
         <v>9</v>
       </c>
       <c r="C14" s="1" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1661,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -1686,7 +1772,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
@@ -1697,7 +1783,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
@@ -1708,7 +1794,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -1718,8 +1804,8 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>84</v>
+      <c r="A7" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>9</v>
@@ -1730,7 +1816,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>9</v>
@@ -1741,7 +1827,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
@@ -1752,7 +1838,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
@@ -1761,21 +1847,21 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" s="7" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5" t="n">
+    <row r="11" s="8" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="6"/>
+      <c r="D11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>9</v>
@@ -1786,7 +1872,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>9</v>
@@ -1797,7 +1883,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>9</v>
@@ -1830,7 +1916,7 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="31.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="18.87"/>
   </cols>
   <sheetData>
@@ -1839,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -1864,7 +1950,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
@@ -1875,7 +1961,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
@@ -1886,7 +1972,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -1896,8 +1982,8 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>96</v>
+      <c r="A7" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>9</v>
@@ -1905,13 +1991,13 @@
       <c r="C7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>97</v>
+      <c r="D7" s="9" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>9</v>
@@ -1922,7 +2008,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
@@ -1933,7 +2019,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
@@ -1943,21 +2029,21 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5" t="n">
+      <c r="A11" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>9</v>
@@ -1968,7 +2054,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>9</v>
@@ -1986,6 +2072,211 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
